--- a/floristics_data/waypoints/waypoint_metadata.xlsx
+++ b/floristics_data/waypoints/waypoint_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gwenr\Documents\Git\junction_floristics\floristics_data\waypoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94778841-34E8-49DF-BC62-57422AEED529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B862127A-3854-45FF-A09C-B9848A19CBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{790ADC43-E4BC-4E32-8116-572E3457ADA7}"/>
   </bookViews>
